--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:53</t>
+    <t xml:space="preserve">2026-09-09 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:41</t>
+    <t xml:space="preserve">2026-09-18 10:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:04</t>
+    <t xml:space="preserve">2026-09-23 12:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:09</t>
+    <t xml:space="preserve">2026-10-02 13:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Tomé</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Mulchén</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:37</t>
+    <t xml:space="preserve">2026-10-04 08:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:27</t>
+    <t xml:space="preserve">2026-10-05 08:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
